--- a/MemberListTemplate.xlsx
+++ b/MemberListTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912FABC8-DC8B-471B-AD95-9F3A2A088434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF2000D-53AA-433B-9EAE-EEA49A3E0BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-180" yWindow="2265" windowWidth="15885" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="First" sheetId="1" r:id="rId1"/>
@@ -138,18 +138,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,13 +442,15 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -473,75 +483,94 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>26658</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>10007</v>
+      </c>
+      <c r="H2">
+        <v>40.712999199999999</v>
+      </c>
+      <c r="I2">
+        <v>-74.013189400000002</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>23196</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>11214</v>
+      </c>
+      <c r="H3">
+        <v>40.597109600000003</v>
+      </c>
+      <c r="I3">
+        <v>-73.986383399999994</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>20028</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>11228</v>
+      </c>
+      <c r="H4">
+        <v>40.610622399999997</v>
+      </c>
+      <c r="I4">
+        <v>-74.008786999999998</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -551,13 +580,15 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -590,75 +621,94 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>26658</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <v>10007</v>
+      </c>
+      <c r="H2">
+        <v>40.712999199999999</v>
+      </c>
+      <c r="I2">
+        <v>-74.013189400000002</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>23196</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>11214</v>
+      </c>
+      <c r="H3">
+        <v>40.597109600000003</v>
+      </c>
+      <c r="I3">
+        <v>-73.986383399999994</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>20028</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>11228</v>
+      </c>
+      <c r="H4">
+        <v>40.610622399999997</v>
+      </c>
+      <c r="I4">
+        <v>-74.008786999999998</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MemberListTemplate.xlsx
+++ b/MemberListTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF2000D-53AA-433B-9EAE-EEA49A3E0BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A5325C-BB1A-4145-90EB-6C68D194E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="First" sheetId="1" r:id="rId1"/>

--- a/MemberListTemplate.xlsx
+++ b/MemberListTemplate.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A5325C-BB1A-4145-90EB-6C68D194E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD9CFD0-4938-45AE-8CC0-AEF6D458308A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="First" sheetId="1" r:id="rId1"/>
     <sheet name="Second" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">First!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Second!$A$1:$I$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -95,6 +99,117 @@
   </si>
   <si>
     <t>Mary Ann Janer</t>
+  </si>
+  <si>
+    <t>Alice Brown</t>
+  </si>
+  <si>
+    <t>1.2.3.5</t>
+  </si>
+  <si>
+    <t>Bob White</t>
+  </si>
+  <si>
+    <t>2.4.6.7</t>
+  </si>
+  <si>
+    <t>Clara Green</t>
+  </si>
+  <si>
+    <t>David Black</t>
+  </si>
+  <si>
+    <t>2.3.5.6</t>
+  </si>
+  <si>
+    <t>Emily White</t>
+  </si>
+  <si>
+    <t>1.4.6</t>
+  </si>
+  <si>
+    <t>Frank Blue</t>
+  </si>
+  <si>
+    <t>2.3.5.7</t>
+  </si>
+  <si>
+    <t>Grace Gray</t>
+  </si>
+  <si>
+    <t>1.2.4.6</t>
+  </si>
+  <si>
+    <t>Henry Gold</t>
+  </si>
+  <si>
+    <t>1.2.3.7</t>
+  </si>
+  <si>
+    <t>Irene Red</t>
+  </si>
+  <si>
+    <t>1.3.6.7</t>
+  </si>
+  <si>
+    <t>Jack Green</t>
+  </si>
+  <si>
+    <t>2.5.7</t>
+  </si>
+  <si>
+    <t>Leo Black</t>
+  </si>
+  <si>
+    <t>1.2.3.6</t>
+  </si>
+  <si>
+    <t>Monica Rose</t>
+  </si>
+  <si>
+    <t>2.4.5</t>
+  </si>
+  <si>
+    <t>1250 67th St</t>
+  </si>
+  <si>
+    <t>W 11th St</t>
+  </si>
+  <si>
+    <t>702 48th St</t>
+  </si>
+  <si>
+    <t>178 28th St</t>
+  </si>
+  <si>
+    <t>855 Franklin Ave</t>
+  </si>
+  <si>
+    <t>833 Marcy Ave</t>
+  </si>
+  <si>
+    <t>585 Schenectady Ave</t>
+  </si>
+  <si>
+    <t>916 E 81st St</t>
+  </si>
+  <si>
+    <t>2099 Kimball St</t>
+  </si>
+  <si>
+    <t>449 Amber St</t>
+  </si>
+  <si>
+    <t>147 Mercer St</t>
+  </si>
+  <si>
+    <t>140 Charles St</t>
+  </si>
+  <si>
+    <t>70 Murry St</t>
+  </si>
+  <si>
+    <t>171 Ridge St</t>
   </si>
 </sst>
 </file>
@@ -118,12 +233,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -138,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -159,6 +280,19 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,7 +573,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
@@ -449,8 +584,8 @@
     <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -475,103 +610,474 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="9">
         <v>26658</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8">
+        <v>11219</v>
+      </c>
+      <c r="H2">
+        <v>40.624946399999999</v>
+      </c>
+      <c r="I2">
+        <v>-74.004250400000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="9">
+        <v>23196</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="8">
+        <v>11223</v>
+      </c>
+      <c r="H3">
+        <v>40.5983163</v>
+      </c>
+      <c r="I3">
+        <v>-73.982652900000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9">
+        <v>20028</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="8">
+        <v>11232</v>
+      </c>
+      <c r="H4">
+        <v>40.658132500000001</v>
+      </c>
+      <c r="I4">
+        <v>-73.999133499999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9">
+        <v>29384</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="8">
+        <v>11220</v>
+      </c>
+      <c r="H5">
+        <v>40.643137199999998</v>
+      </c>
+      <c r="I5">
+        <v>-74.004804899999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="9">
+        <v>27474</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="8">
+        <v>11225</v>
+      </c>
+      <c r="H6">
+        <v>40.6692161</v>
+      </c>
+      <c r="I6">
+        <v>-73.958326900000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="9">
+        <v>33191</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="8">
+        <v>11216</v>
+      </c>
+      <c r="H7">
+        <v>40.684881099999998</v>
+      </c>
+      <c r="I7">
+        <v>-73.946805999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="9">
+        <v>31146</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
+        <v>11203</v>
+      </c>
+      <c r="H8">
+        <v>40.659804600000001</v>
+      </c>
+      <c r="I8">
+        <v>-73.933204399999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="9">
+        <v>34961</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="8">
+        <v>11236</v>
+      </c>
+      <c r="H9">
+        <v>40.635496799999999</v>
+      </c>
+      <c r="I9">
+        <v>-73.912332899999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="9">
+        <v>26328</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="8">
+        <v>11234</v>
+      </c>
+      <c r="H10">
+        <v>40.610126999999999</v>
+      </c>
+      <c r="I10">
+        <v>-73.926663000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="9">
+        <v>32360</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="8">
+        <v>11208</v>
+      </c>
+      <c r="H11">
+        <v>40.667362099999998</v>
+      </c>
+      <c r="I11">
+        <v>-73.857241599999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="9">
+        <v>25184</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G12" s="8">
+        <v>10012</v>
+      </c>
+      <c r="H12">
+        <v>40.724912199999999</v>
+      </c>
+      <c r="I12">
+        <v>-73.998643400000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="9">
+        <v>33749</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="8">
+        <v>10014</v>
+      </c>
+      <c r="H13">
+        <v>40.734034399999999</v>
+      </c>
+      <c r="I13">
+        <v>-74.008344699999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="9">
+        <v>30975</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="8">
         <v>10007</v>
       </c>
-      <c r="H2">
-        <v>40.712999199999999</v>
-      </c>
-      <c r="I2">
-        <v>-74.013189400000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4">
-        <v>23196</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="H14">
+        <v>44.830970899999997</v>
+      </c>
+      <c r="I14">
+        <v>-74.714714400000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="9">
+        <v>29315</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="8">
+        <v>10002</v>
+      </c>
+      <c r="H15">
+        <v>40.720425200000001</v>
+      </c>
+      <c r="I15">
+        <v>-73.982560899999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3">
-        <v>11214</v>
-      </c>
-      <c r="H3">
-        <v>40.597109600000003</v>
-      </c>
-      <c r="I3">
-        <v>-73.986383399999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4">
-        <v>20028</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3">
-        <v>11228</v>
-      </c>
-      <c r="H4">
-        <v>40.610622399999997</v>
-      </c>
-      <c r="I4">
-        <v>-74.008786999999998</v>
-      </c>
+      <c r="B16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="9">
+        <v>33065</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="8">
+        <v>10002</v>
+      </c>
+      <c r="H16">
+        <v>40.720425200000001</v>
+      </c>
+      <c r="I16">
+        <v>-73.982560899999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A1:I16" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="1.2.3.4.5.6.7"/>
+        <filter val="1.2.3.6"/>
+        <filter val="1.2.4.6"/>
+        <filter val="1.3.6.7"/>
+        <filter val="1.4.6"/>
+        <filter val="2.3.5.6"/>
+        <filter val="2.4.6.7"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -587,8 +1093,8 @@
     <col min="5" max="5" width="20.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -613,10 +1119,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
@@ -708,7 +1214,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <autoFilter ref="A1:I1" xr:uid="{37E4A800-C376-4B9C-BDA9-DD2DF99A2191}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MemberListTemplate.xlsx
+++ b/MemberListTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASCC\Desktop\driverclusters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD9CFD0-4938-45AE-8CC0-AEF6D458308A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480FBCFF-B1DA-49BC-A842-097BFCB125D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="First" sheetId="1" r:id="rId1"/>
